--- a/fixtures/acceptance/T12_empty_change_request/Output/ChangeLog_T12_RUN.xlsx
+++ b/fixtures/acceptance/T12_empty_change_request/Output/ChangeLog_T12_RUN.xlsx
@@ -8,8 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChangeLog_Detail" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conflicts" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conflicts" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -529,72 +528,6 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>change_request_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>table_name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>change_type</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>n_keys_before</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>n_keys_after</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>key_tuple</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>column_name</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>old_value</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>new_value</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
           <t>conflict_type</t>
         </is>
       </c>

--- a/fixtures/acceptance/T12_empty_change_request/Output/ChangeLog_T12_RUN.xlsx
+++ b/fixtures/acceptance/T12_empty_change_request/Output/ChangeLog_T12_RUN.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conflicts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReviewFiles" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -580,4 +581,35 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>table_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>review_file</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>